--- a/module-3/RBruetzmann - Assignment 3.2.xlsx
+++ b/module-3/RBruetzmann - Assignment 3.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Bob/csd/CSD-310/module-3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C8FF46-405F-604C-8E43-218EA76EDCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67395A9D-7FB1-F140-9DCD-3D5162448C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4760" yWindow="2160" windowWidth="24900" windowHeight="17220" xr2:uid="{D7D6554E-156B-F949-9213-C480D9F4F601}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>First Normal Form Table</t>
   </si>
@@ -86,9 +86,6 @@
     <t>book_price</t>
   </si>
   <si>
-    <t>author_email</t>
-  </si>
-  <si>
     <t>Book Table</t>
   </si>
   <si>
@@ -101,12 +98,6 @@
     <t>publisher_name</t>
   </si>
   <si>
-    <t>publisher_address</t>
-  </si>
-  <si>
-    <t>publisher_email</t>
-  </si>
-  <si>
     <t>Author Table</t>
   </si>
   <si>
@@ -116,12 +107,6 @@
     <t>author_lastname</t>
   </si>
   <si>
-    <t>author_phone</t>
-  </si>
-  <si>
-    <t>author_address</t>
-  </si>
-  <si>
     <t>author_ID</t>
   </si>
   <si>
@@ -131,9 +116,6 @@
     <t>Third Normal Form Tables</t>
   </si>
   <si>
-    <t>author_zipcode</t>
-  </si>
-  <si>
     <t>Breutzmann, Robert</t>
   </si>
   <si>
@@ -141,6 +123,36 @@
   </si>
   <si>
     <t>Due Date - 11/9/2025</t>
+  </si>
+  <si>
+    <t>contact_ID</t>
+  </si>
+  <si>
+    <t>publisher_contact_ID</t>
+  </si>
+  <si>
+    <t>author_contact_ID</t>
+  </si>
+  <si>
+    <t>street_address</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>zipcode</t>
+  </si>
+  <si>
+    <t>Contact Information Table</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>email</t>
   </si>
 </sst>
 </file>
@@ -177,20 +189,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color theme="1"/>
+      <sz val="12"/>
+      <color theme="8" tint="-0.249977111117893"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,8 +229,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -304,35 +324,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -342,15 +418,48 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -372,16 +481,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>787400</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -396,8 +505,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6870700" y="2781300"/>
-          <a:ext cx="7239000" cy="2628900"/>
+          <a:off x="7366000" y="2616200"/>
+          <a:ext cx="6108700" cy="5867400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -447,7 +556,7 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> assuming that each book has one author and. publisher.  In the real world, this is not always the case. (though a second publisher of a book typically has a second ISBN)</a:t>
+            <a:t> assuming that each book has one author and. publisher.  In the real world, this is not always the case. (though a second publisher of a book typically has a second ISBN).  To solve this, you would need to use a transitive table (explained later) that can link the book_isbn to author_ID.  But for this example, I'm sticking with one-to-many relatiomship of one author per book.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -456,7 +565,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>The Author tab dynamically generates an author ID.  An email could potentially be shared between two people and have different authors (husband and wife sharing an email, both authors for example, so it is not unique), so an author ID will be generated by the table to be referanced.</a:t>
+            <a:t>The Author table dynamically generates an author ID.  None of the information is 100% to be unique to a single author. An email could potentially be shared between two people and have different authors (husband and wife sharing an email, both authors for example, so it is not unique), same with a physical address.  A name can obviously be shared especialy common names, so an author ID will be generated by the table to be referanced.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -498,6 +607,30 @@
           <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" baseline="0"/>
         </a:p>
         <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0"/>
+            <a:t>Also, I separeated the address into streetaddress (left with the label address), city, state, and zipcode so that they are independently searchable.  I thought about leaving out city/state and only using zipcode, but there are cities that use multiple zipcodes, and zipcodes that cover multiple cities so I didn't want to do this.  This makes the "address" entry more atomic, instead of being 4 seperate entries.  </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0"/>
+            <a:t>Finally, I made a seperate table for contact information.  This may not be necessary, but could have advantages in very large datasets wher publishers and authors may start to overlap or have multiple contact information. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0"/>
+            <a:t>From a little researching, I learned a bit about a transitive table, where you have a table that "joins" two others that is used for many to many relationships.  For exmaple, this table would be authors/publisherID and Contact ID for their keys, and it links an author or publisher to a contact.  In this way, you can link each author to as many contacts as you like, or a contact to as many authors as you like.  It does add more queries however so it's a trade off that may not be worth it in a smaller system.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
           <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
         </a:p>
         <a:p>
@@ -530,14 +663,14 @@
     <tableColumn id="1" xr3:uid="{7753819C-8CB5-F347-B756-DD6E15AEF7C0}" name="Publisher Name"/>
     <tableColumn id="2" xr3:uid="{CFAD4652-DC9D-BC4A-B453-C7F024D95C65}" name="Publisher ID"/>
     <tableColumn id="3" xr3:uid="{0112A26E-17A5-3448-9DBF-CBB721558D58}" name="Publisher Address"/>
-    <tableColumn id="4" xr3:uid="{31DF7868-5413-414A-B983-01DD4B599AC3}" name="Book ISBN"/>
-    <tableColumn id="5" xr3:uid="{66B47A84-1C09-7D40-BB72-73999695F2A8}" name="Book Name"/>
-    <tableColumn id="6" xr3:uid="{0A18359D-9800-D143-A5C6-511F19255273}" name="Book Price"/>
-    <tableColumn id="7" xr3:uid="{20A7F9D4-D46D-4B4A-8D97-07CD40CFAD9A}" name="Author First Name"/>
-    <tableColumn id="8" xr3:uid="{E9196836-E170-C34D-95E4-E7AC4A78002C}" name="Author Last Name"/>
-    <tableColumn id="9" xr3:uid="{31120C25-668E-AE41-91CB-B482FFA7F6DE}" name="Author Phone"/>
-    <tableColumn id="10" xr3:uid="{3FD07E9F-60B9-464B-BB04-E1E484DE1032}" name="Author Email"/>
-    <tableColumn id="11" xr3:uid="{8A188A73-5509-684A-A7AE-610CCC5A7408}" name="Publisher Email"/>
+    <tableColumn id="4" xr3:uid="{31DF7868-5413-414A-B983-01DD4B599AC3}" name="Publisher Email"/>
+    <tableColumn id="5" xr3:uid="{66B47A84-1C09-7D40-BB72-73999695F2A8}" name="Book ISBN"/>
+    <tableColumn id="6" xr3:uid="{0A18359D-9800-D143-A5C6-511F19255273}" name="Book Name"/>
+    <tableColumn id="7" xr3:uid="{20A7F9D4-D46D-4B4A-8D97-07CD40CFAD9A}" name="Book Price"/>
+    <tableColumn id="8" xr3:uid="{E9196836-E170-C34D-95E4-E7AC4A78002C}" name="Author First Name"/>
+    <tableColumn id="9" xr3:uid="{31120C25-668E-AE41-91CB-B482FFA7F6DE}" name="Author Last Name"/>
+    <tableColumn id="10" xr3:uid="{3FD07E9F-60B9-464B-BB04-E1E484DE1032}" name="Author Phone"/>
+    <tableColumn id="11" xr3:uid="{8A188A73-5509-684A-A7AE-610CCC5A7408}" name="Author Email"/>
     <tableColumn id="12" xr3:uid="{8900E7F5-4793-DD4F-B1BB-A3925C0FD179}" name="Author Address"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -861,110 +994,221 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C549B3EC-E671-BF41-9304-8C5A8FDBCDAC}">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.1640625" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" customWidth="1"/>
-    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" customWidth="1"/>
-    <col min="9" max="9" width="14.1640625" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="15.83203125" customWidth="1"/>
-    <col min="12" max="12" width="15.5" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A1" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>34</v>
-      </c>
+      <c r="A2" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+    </row>
+    <row r="3" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
     </row>
     <row r="4" spans="1:12" ht="27" x14ac:dyDescent="0.35">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="K5" t="s">
-        <v>11</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="L5" s="4" t="s">
         <v>12</v>
       </c>
     </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="3"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="4"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="3"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="4"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="3"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="4"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="3"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="4"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="3"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="4"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="3"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="4"/>
+    </row>
+    <row r="12" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="9"/>
+    </row>
     <row r="14" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:12" ht="27" x14ac:dyDescent="0.35">
-      <c r="A15" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:12" ht="22" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="25"/>
+    <row r="15" spans="1:12" ht="28" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="33"/>
+    </row>
+    <row r="16" spans="1:12" ht="23" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="14"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -972,21 +1216,23 @@
       <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>28</v>
-      </c>
+      <c r="D17" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="4"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -994,8 +1240,13 @@
       <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="10"/>
-      <c r="E18" s="11"/>
+      <c r="A18" s="3"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="4"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1003,13 +1254,15 @@
       <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" ht="22" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="25"/>
+      <c r="A19" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="30"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1017,19 +1270,19 @@
       <c r="L19" s="1"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="11"/>
+      <c r="C20" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="4"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1037,8 +1290,13 @@
       <c r="L20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="10"/>
-      <c r="E21" s="11"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="4"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1046,13 +1304,15 @@
       <c r="L21" s="1"/>
     </row>
     <row r="22" spans="1:12" ht="22" x14ac:dyDescent="0.3">
-      <c r="A22" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="25"/>
+      <c r="A22" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="30"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1060,66 +1320,99 @@
       <c r="L22" s="1"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>26</v>
-      </c>
+      <c r="A23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="24"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="4"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="18"/>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="4"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="22" x14ac:dyDescent="0.3">
+      <c r="A25" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="30"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
+    <row r="26" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="E31" s="18"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="E32" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/module-3/RBruetzmann - Assignment 3.2.xlsx
+++ b/module-3/RBruetzmann - Assignment 3.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Bob/csd/CSD-310/module-3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67395A9D-7FB1-F140-9DCD-3D5162448C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FB3C47-BD4B-C440-BD4A-0B929BEA1636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4760" yWindow="2160" windowWidth="24900" windowHeight="17220" xr2:uid="{D7D6554E-156B-F949-9213-C480D9F4F601}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="96">
   <si>
     <t>First Normal Form Table</t>
   </si>
@@ -153,6 +153,177 @@
   </si>
   <si>
     <t>email</t>
+  </si>
+  <si>
+    <t>Penguin Random House</t>
+  </si>
+  <si>
+    <t>PUB001</t>
+  </si>
+  <si>
+    <t>1745 Broadway, New York, NY 10019</t>
+  </si>
+  <si>
+    <t>info@penguinrandomhouse.com</t>
+  </si>
+  <si>
+    <t>The Martian</t>
+  </si>
+  <si>
+    <t>Andy</t>
+  </si>
+  <si>
+    <t>Weir</t>
+  </si>
+  <si>
+    <t>555-234-1111</t>
+  </si>
+  <si>
+    <t>andy.weir@email.com</t>
+  </si>
+  <si>
+    <t>100 Main St, Mountain View, CA 94040</t>
+  </si>
+  <si>
+    <t>HarperCollins</t>
+  </si>
+  <si>
+    <t>PUB002</t>
+  </si>
+  <si>
+    <t>195 Broadway, New York, NY 10007</t>
+  </si>
+  <si>
+    <t>contact@harpercollins.com</t>
+  </si>
+  <si>
+    <t>The Alchemist</t>
+  </si>
+  <si>
+    <t>Paulo</t>
+  </si>
+  <si>
+    <t>Coelho</t>
+  </si>
+  <si>
+    <t>555-234-2222</t>
+  </si>
+  <si>
+    <t>paulo.coelho@email.com</t>
+  </si>
+  <si>
+    <t>Rio de Janeiro, Brazil</t>
+  </si>
+  <si>
+    <t>O’Reilly Media</t>
+  </si>
+  <si>
+    <t>PUB003</t>
+  </si>
+  <si>
+    <t>1005 Gravenstein Hwy N, Sebastopol, CA 95472</t>
+  </si>
+  <si>
+    <t>info@oreilly.com</t>
+  </si>
+  <si>
+    <t>Learning SQL</t>
+  </si>
+  <si>
+    <t>Alan</t>
+  </si>
+  <si>
+    <t>Beaulieu</t>
+  </si>
+  <si>
+    <t>555-234-3333</t>
+  </si>
+  <si>
+    <t>alan.beaulieu@email.com</t>
+  </si>
+  <si>
+    <t>42 Oak St, Sebastopol, CA 95472</t>
+  </si>
+  <si>
+    <t>Addison-Wesley</t>
+  </si>
+  <si>
+    <t>PUB004</t>
+  </si>
+  <si>
+    <t>75 Arlington St, Boston, MA 02116</t>
+  </si>
+  <si>
+    <t>info@addisonwesley.com</t>
+  </si>
+  <si>
+    <t>Effective Java</t>
+  </si>
+  <si>
+    <t>Joshua</t>
+  </si>
+  <si>
+    <t>Bloch</t>
+  </si>
+  <si>
+    <t>555-234-4444</t>
+  </si>
+  <si>
+    <t>joshua.bloch@email.com</t>
+  </si>
+  <si>
+    <t>10 Park Ave, Princeton, NJ 08540</t>
+  </si>
+  <si>
+    <t>Sams Publishing</t>
+  </si>
+  <si>
+    <t>PUB005</t>
+  </si>
+  <si>
+    <t>800 East 96th St, Indianapolis, IN 46240</t>
+  </si>
+  <si>
+    <t>support@sams.com</t>
+  </si>
+  <si>
+    <t>SQL in 10 Minutes</t>
+  </si>
+  <si>
+    <t>Ben</t>
+  </si>
+  <si>
+    <t>Forta</t>
+  </si>
+  <si>
+    <t>555-234-5555</t>
+  </si>
+  <si>
+    <t>ben.forta@email.com</t>
+  </si>
+  <si>
+    <t>22 Lake Rd, Miami, FL 33101</t>
+  </si>
+  <si>
+    <t>Harry Potter and the Sorcerer's Stone</t>
+  </si>
+  <si>
+    <t>J.K.</t>
+  </si>
+  <si>
+    <t>Rowling</t>
+  </si>
+  <si>
+    <t>555-234-6666</t>
+  </si>
+  <si>
+    <t>jk.rowling@email.com</t>
+  </si>
+  <si>
+    <t>Edinburgh, Scotland</t>
+  </si>
+  <si>
+    <t>Harry Potter and the Chamber of Secrets</t>
   </si>
 </sst>
 </file>
@@ -409,46 +580,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -459,12 +602,44 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -481,16 +656,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>787400</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1689100</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -505,8 +680,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7366000" y="2616200"/>
-          <a:ext cx="6108700" cy="5867400"/>
+          <a:off x="2070100" y="6134100"/>
+          <a:ext cx="8534400" cy="5867400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -634,6 +809,33 @@
           <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
         </a:p>
         <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>I used ChatGPT to fill in the table with fake data.  I asked it to have a couple repeat publishers and a couple repeat authors for the table.  Citation below.  The tables are 100% my work.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t>OpenAI. (2025, November 5). </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" i="1"/>
+            <a:t>Conversation with ChatGPT for fake data for a 1NF table.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t> ChatGPT. </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US">
+              <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id=""/>
+            </a:rPr>
+            <a:t>https://chat.openai.com/</a:t>
+          </a:r>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -664,7 +866,7 @@
     <tableColumn id="2" xr3:uid="{CFAD4652-DC9D-BC4A-B453-C7F024D95C65}" name="Publisher ID"/>
     <tableColumn id="3" xr3:uid="{0112A26E-17A5-3448-9DBF-CBB721558D58}" name="Publisher Address"/>
     <tableColumn id="4" xr3:uid="{31DF7868-5413-414A-B983-01DD4B599AC3}" name="Publisher Email"/>
-    <tableColumn id="5" xr3:uid="{66B47A84-1C09-7D40-BB72-73999695F2A8}" name="Book ISBN"/>
+    <tableColumn id="5" xr3:uid="{66B47A84-1C09-7D40-BB72-73999695F2A8}" name="Book ISBN" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{0A18359D-9800-D143-A5C6-511F19255273}" name="Book Name"/>
     <tableColumn id="7" xr3:uid="{20A7F9D4-D46D-4B4A-8D97-07CD40CFAD9A}" name="Book Price"/>
     <tableColumn id="8" xr3:uid="{E9196836-E170-C34D-95E4-E7AC4A78002C}" name="Author First Name"/>
@@ -994,95 +1196,95 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C549B3EC-E671-BF41-9304-8C5A8FDBCDAC}">
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
     </row>
     <row r="3" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
     </row>
     <row r="4" spans="1:12" ht="27" x14ac:dyDescent="0.35">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="12"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="32"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" t="s">
         <v>10</v>
       </c>
       <c r="L5" s="4" t="s">
@@ -1090,125 +1292,293 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="4"/>
+      <c r="A6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="33">
+        <v>9780143127741</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6">
+        <v>14.99</v>
+      </c>
+      <c r="H6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="4"/>
+      <c r="A7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="33">
+        <v>9780062316097</v>
+      </c>
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="H7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="4"/>
+      <c r="A8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="33">
+        <v>9781491957660</v>
+      </c>
+      <c r="F8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8">
+        <v>39.99</v>
+      </c>
+      <c r="H8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="4"/>
+      <c r="A9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="33">
+        <v>9780134685991</v>
+      </c>
+      <c r="F9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9">
+        <v>54.99</v>
+      </c>
+      <c r="H9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="4"/>
+      <c r="A10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="33">
+        <v>9780672336072</v>
+      </c>
+      <c r="F10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10">
+        <v>24.99</v>
+      </c>
+      <c r="H10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" t="s">
+        <v>85</v>
+      </c>
+      <c r="J10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K10" t="s">
+        <v>87</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="3"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="4"/>
+      <c r="A11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="33">
+        <v>9780590353427</v>
+      </c>
+      <c r="F11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11">
+        <v>12.99</v>
+      </c>
+      <c r="H11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" t="s">
+        <v>91</v>
+      </c>
+      <c r="J11" t="s">
+        <v>92</v>
+      </c>
+      <c r="K11" t="s">
+        <v>93</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="12" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="9"/>
+      <c r="A12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="34">
+        <v>9780590353434</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="8">
+        <v>13.99</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="14" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:12" ht="28" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="33"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="23"/>
     </row>
     <row r="16" spans="1:12" ht="23" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="14"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="26"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1219,19 +1589,18 @@
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="18"/>
       <c r="G17" s="4"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1241,11 +1610,6 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="3"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
       <c r="G18" s="4"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1254,15 +1618,15 @@
       <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" ht="22" x14ac:dyDescent="0.3">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="30"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1273,15 +1637,12 @@
       <c r="A20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="18"/>
       <c r="G20" s="4"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1291,11 +1652,6 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
       <c r="G21" s="4"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -1304,15 +1660,15 @@
       <c r="L21" s="1"/>
     </row>
     <row r="22" spans="1:12" ht="22" x14ac:dyDescent="0.3">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="30"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="29"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1323,17 +1679,15 @@
       <c r="A23" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="34" t="s">
+      <c r="D23" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="24"/>
-      <c r="F23" s="18"/>
       <c r="G23" s="4"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1345,11 +1699,6 @@
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="18"/>
       <c r="G24" s="4"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -1358,61 +1707,54 @@
       <c r="L24" s="1"/>
     </row>
     <row r="25" spans="1:12" ht="22" x14ac:dyDescent="0.3">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="1"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="29"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
     </row>
     <row r="26" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D26" s="26" t="s">
+      <c r="D26" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E26" s="26" t="s">
+      <c r="E26" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="27" t="s">
+      <c r="G26" s="18" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E31" s="18"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E32" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A4:L4"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
